--- a/ECM_fitting_results_advanced.xlsx
+++ b/ECM_fitting_results_advanced.xlsx
@@ -450,17 +450,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>rmse</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>AIC</t>
+          <t>aic</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>bic</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
